--- a/testdata/OpenCart-TestCases.xlsx
+++ b/testdata/OpenCart-TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjectClonned\opencartPlaywrightPythonFramework\opencartPlaywrightPythonFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B20AC5D-BF81-4D07-AED7-4AC6C74A460B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F56F20-514C-4067-A21B-AA978AC25187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="914" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4136" uniqueCount="2147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4138" uniqueCount="2148">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -8203,6 +8203,9 @@
   </si>
   <si>
     <t>TC005_EmptyEmailAndPasswordClickLoginButton</t>
+  </si>
+  <si>
+    <t>TC006_Forgotten_Password_Link_Present</t>
   </si>
 </sst>
 </file>
@@ -8577,7 +8580,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8789,6 +8792,16 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -20898,31 +20911,33 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="126" x14ac:dyDescent="0.65">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="40" t="s">
         <v>1165</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="40" t="s">
         <v>1161</v>
       </c>
-      <c r="E7" s="70" t="s">
+      <c r="E7" s="40" t="s">
         <v>1883</v>
       </c>
-      <c r="F7" s="68" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="70" t="s">
+      <c r="F7" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="71"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="83"/>
+      <c r="K7" s="66" t="s">
+        <v>2135</v>
+      </c>
       <c r="L7" s="67" t="s">
         <v>2146</v>
       </c>
@@ -20953,7 +20968,9 @@
       <c r="I8" s="71"/>
       <c r="J8" s="72"/>
       <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
+      <c r="L8" s="67" t="s">
+        <v>2147</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="210" x14ac:dyDescent="0.65">
       <c r="A9" s="68" t="s">

--- a/testdata/OpenCart-TestCases.xlsx
+++ b/testdata/OpenCart-TestCases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjectClonned\opencartPlaywrightPythonFramework\opencartPlaywrightPythonFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F56F20-514C-4067-A21B-AA978AC25187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF33672-68BD-4124-800C-151AB1837A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="914" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vesion History" sheetId="2" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4138" uniqueCount="2148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4147" uniqueCount="2157">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -8206,6 +8206,33 @@
   </si>
   <si>
     <t>TC006_Forgotten_Password_Link_Present</t>
+  </si>
+  <si>
+    <t>Register</t>
+  </si>
+  <si>
+    <t>1.After git push automatic run</t>
+  </si>
+  <si>
+    <t>2.Email Configuration</t>
+  </si>
+  <si>
+    <t>5.Execution from Azure</t>
+  </si>
+  <si>
+    <t>4.kubernatics</t>
+  </si>
+  <si>
+    <t>3.docker</t>
+  </si>
+  <si>
+    <t>6.Execution from Azure</t>
+  </si>
+  <si>
+    <t>7.Multimpe Environment Execution</t>
+  </si>
+  <si>
+    <t>Additional Implementation</t>
   </si>
 </sst>
 </file>
@@ -8580,7 +8607,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8775,6 +8802,16 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -8793,15 +8830,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9954,7 +9985,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88C1DAE7-A63C-4B04-BE99-C7C19B2E05F2}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="21" x14ac:dyDescent="0.65"/>
   <cols>
     <col min="1" max="1" width="33.9296875" style="20" customWidth="1"/>
@@ -9964,12 +9995,12 @@
     <col min="6" max="6" width="12.33203125" style="20" customWidth="1"/>
     <col min="7" max="7" width="13" style="20" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" style="20" customWidth="1"/>
-    <col min="9" max="9" width="11.46484375" style="20" customWidth="1"/>
+    <col min="9" max="9" width="68.9296875" style="20" customWidth="1"/>
     <col min="10" max="10" width="13.19921875" style="20" customWidth="1"/>
     <col min="11" max="16384" width="8.73046875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A1" s="36" t="s">
         <v>14</v>
       </c>
@@ -9977,14 +10008,17 @@
         <v>1127</v>
       </c>
       <c r="C1" s="35"/>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="85" t="s">
         <v>2138</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="85" t="s">
         <v>2139</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.65">
+      <c r="I1" s="71" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A2" s="38" t="s">
         <v>6</v>
       </c>
@@ -9992,38 +10026,69 @@
         <v>1128</v>
       </c>
       <c r="C2" s="35"/>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="85" t="s">
         <v>2140</v>
       </c>
-      <c r="G2" s="35">
+      <c r="G2" s="85">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.65">
-      <c r="A3" s="75" t="s">
+      <c r="I2" s="71" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="A3" s="79" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="39" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="39"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.65">
-      <c r="A4" s="76"/>
+      <c r="F3" s="71" t="s">
+        <v>2148</v>
+      </c>
+      <c r="G3" s="71"/>
+      <c r="I3" s="71" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="A4" s="80"/>
       <c r="B4" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="39" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.65">
-      <c r="A5" s="76"/>
-      <c r="B5" s="39" t="s">
+      <c r="I4" s="71" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="A5" s="80"/>
+      <c r="B5" s="85" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="39" t="s">
         <v>19</v>
+      </c>
+      <c r="I5" s="71" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="I6" s="71" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="I7" s="71" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="I8" s="84" t="s">
+        <v>2155</v>
       </c>
     </row>
   </sheetData>
@@ -10090,10 +10155,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -10434,10 +10499,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -11047,10 +11112,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -12039,10 +12104,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -12411,10 +12476,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -13053,10 +13118,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -13398,10 +13463,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -13851,10 +13916,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -14304,10 +14369,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -14973,10 +15038,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -15367,10 +15432,10 @@
       <c r="A2" s="42" t="s">
         <v>1076</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="82" t="s">
         <v>1126</v>
       </c>
-      <c r="C2" s="79"/>
+      <c r="C2" s="83"/>
       <c r="D2" s="41"/>
       <c r="E2" s="41"/>
     </row>
@@ -15378,10 +15443,10 @@
       <c r="A3" s="42" t="s">
         <v>1077</v>
       </c>
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="82" t="s">
         <v>1127</v>
       </c>
-      <c r="C3" s="79"/>
+      <c r="C3" s="83"/>
       <c r="D3" s="41"/>
       <c r="E3" s="41"/>
     </row>
@@ -15389,10 +15454,10 @@
       <c r="A4" s="42" t="s">
         <v>1078</v>
       </c>
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="83" t="s">
         <v>2130</v>
       </c>
-      <c r="C4" s="79"/>
+      <c r="C4" s="83"/>
       <c r="D4" s="41"/>
       <c r="E4" s="41"/>
     </row>
@@ -15400,10 +15465,10 @@
       <c r="A5" s="42" t="s">
         <v>1079</v>
       </c>
-      <c r="B5" s="79" t="s">
+      <c r="B5" s="83" t="s">
         <v>1128</v>
       </c>
-      <c r="C5" s="79"/>
+      <c r="C5" s="83"/>
       <c r="D5" s="41"/>
       <c r="E5" s="41"/>
     </row>
@@ -15411,10 +15476,10 @@
       <c r="A6" s="44" t="s">
         <v>1080</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="81" t="s">
         <v>2132</v>
       </c>
-      <c r="C6" s="77"/>
+      <c r="C6" s="81"/>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
       <c r="F6" s="46"/>
@@ -15423,10 +15488,10 @@
       <c r="A7" s="44" t="s">
         <v>1081</v>
       </c>
-      <c r="B7" s="77" t="s">
+      <c r="B7" s="81" t="s">
         <v>2132</v>
       </c>
-      <c r="C7" s="77"/>
+      <c r="C7" s="81"/>
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
       <c r="F7" s="46"/>
@@ -16135,10 +16200,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -16452,10 +16517,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -16850,10 +16915,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -17302,10 +17367,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -17673,10 +17738,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -18233,10 +18298,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -18631,10 +18696,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -18975,10 +19040,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -19859,10 +19924,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -20311,10 +20376,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -20768,10 +20833,10 @@
       </c>
     </row>
     <row r="2" spans="1:12" s="21" customFormat="1" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -20911,10 +20976,10 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="126" x14ac:dyDescent="0.65">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="81" t="s">
+      <c r="B7" s="75" t="s">
         <v>99</v>
       </c>
       <c r="C7" s="40" t="s">
@@ -20926,15 +20991,15 @@
       <c r="E7" s="40" t="s">
         <v>1883</v>
       </c>
-      <c r="F7" s="80" t="s">
+      <c r="F7" s="74" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="83"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="77"/>
       <c r="K7" s="66" t="s">
         <v>2135</v>
       </c>
@@ -21534,10 +21599,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -21931,10 +21996,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -22464,10 +22529,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -23159,10 +23224,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -23341,10 +23406,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -24174,10 +24239,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="19" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -24574,10 +24639,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -25349,10 +25414,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -26044,10 +26109,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -26797,10 +26862,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.65">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>1094</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>

--- a/testdata/OpenCart-TestCases.xlsx
+++ b/testdata/OpenCart-TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjectClonned\opencartPlaywrightPythonFramework\opencartPlaywrightPythonFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF33672-68BD-4124-800C-151AB1837A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C318D14-3110-4E52-A2F3-591F21FECC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4147" uniqueCount="2157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4148" uniqueCount="2158">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -8211,9 +8211,6 @@
     <t>Register</t>
   </si>
   <si>
-    <t>1.After git push automatic run</t>
-  </si>
-  <si>
     <t>2.Email Configuration</t>
   </si>
   <si>
@@ -8233,6 +8230,12 @@
   </si>
   <si>
     <t>Additional Implementation</t>
+  </si>
+  <si>
+    <t>1.After git push automatic run - github Actions --Playwright</t>
+  </si>
+  <si>
+    <t>8.After git push automatic run from Jenkins</t>
   </si>
 </sst>
 </file>
@@ -8376,7 +8379,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8410,6 +8413,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -8607,7 +8616,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8834,6 +8843,7 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9985,7 +9995,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88C1DAE7-A63C-4B04-BE99-C7C19B2E05F2}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="21" x14ac:dyDescent="0.65"/>
   <cols>
     <col min="1" max="1" width="33.9296875" style="20" customWidth="1"/>
@@ -9995,7 +10005,7 @@
     <col min="6" max="6" width="12.33203125" style="20" customWidth="1"/>
     <col min="7" max="7" width="13" style="20" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" style="20" customWidth="1"/>
-    <col min="9" max="9" width="68.9296875" style="20" customWidth="1"/>
+    <col min="9" max="9" width="71.6640625" style="20" customWidth="1"/>
     <col min="10" max="10" width="13.19921875" style="20" customWidth="1"/>
     <col min="11" max="16384" width="8.73046875" style="20"/>
   </cols>
@@ -10015,7 +10025,7 @@
         <v>2139</v>
       </c>
       <c r="I1" s="71" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.65">
@@ -10032,8 +10042,8 @@
       <c r="G2" s="85">
         <v>23</v>
       </c>
-      <c r="I2" s="71" t="s">
-        <v>2149</v>
+      <c r="I2" s="86" t="s">
+        <v>2156</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.65">
@@ -10049,7 +10059,7 @@
       </c>
       <c r="G3" s="71"/>
       <c r="I3" s="71" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.65">
@@ -10061,7 +10071,7 @@
         <v>17</v>
       </c>
       <c r="I4" s="71" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.65">
@@ -10073,22 +10083,27 @@
         <v>19</v>
       </c>
       <c r="I5" s="71" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.65">
       <c r="I6" s="71" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.65">
       <c r="I7" s="71" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.65">
       <c r="I8" s="84" t="s">
-        <v>2155</v>
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="I9" s="71" t="s">
+        <v>2157</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/OpenCart-TestCases.xlsx
+++ b/testdata/OpenCart-TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjectClonned\opencartPlaywrightPythonFramework\opencartPlaywrightPythonFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C318D14-3110-4E52-A2F3-591F21FECC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F154F355-C130-4575-94BC-D7FB4CBAAD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4148" uniqueCount="2158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="2159">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -8236,6 +8236,9 @@
   </si>
   <si>
     <t>8.After git push automatic run from Jenkins</t>
+  </si>
+  <si>
+    <t>CodeGen--Playwright Feature -- Not AI Feaature</t>
   </si>
 </sst>
 </file>
@@ -9995,7 +9998,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88C1DAE7-A63C-4B04-BE99-C7C19B2E05F2}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="21" x14ac:dyDescent="0.65"/>
   <cols>
     <col min="1" max="1" width="33.9296875" style="20" customWidth="1"/>
@@ -10102,8 +10105,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.65">
-      <c r="I9" s="71" t="s">
+      <c r="I9" s="86" t="s">
         <v>2157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="I14" s="20" t="s">
+        <v>2158</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/OpenCart-TestCases.xlsx
+++ b/testdata/OpenCart-TestCases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjectClonned\opencartPlaywrightPythonFramework\opencartPlaywrightPythonFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F154F355-C130-4575-94BC-D7FB4CBAAD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7004C379-CCF8-491D-9E88-5634EDE2E2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="914" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vesion History" sheetId="2" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="2159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4152" uniqueCount="2160">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -8239,6 +8239,9 @@
   </si>
   <si>
     <t>CodeGen--Playwright Feature -- Not AI Feaature</t>
+  </si>
+  <si>
+    <t>TC007_LoginUsingKeyboardKey</t>
   </si>
 </sst>
 </file>
@@ -21031,31 +21034,33 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="105" x14ac:dyDescent="0.65">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="40" t="s">
         <v>1166</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="D8" s="40" t="s">
         <v>1161</v>
       </c>
-      <c r="E8" s="70" t="s">
+      <c r="E8" s="40" t="s">
         <v>1868</v>
       </c>
-      <c r="F8" s="68" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="70" t="s">
+      <c r="F8" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="71"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="66" t="s">
+        <v>2135</v>
+      </c>
       <c r="L8" s="67" t="s">
         <v>2147</v>
       </c>
@@ -21085,8 +21090,12 @@
       <c r="H9" s="71"/>
       <c r="I9" s="71"/>
       <c r="J9" s="72"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="71"/>
+      <c r="K9" s="66" t="s">
+        <v>2135</v>
+      </c>
+      <c r="L9" s="67" t="s">
+        <v>2159</v>
+      </c>
     </row>
     <row r="10" spans="1:12" ht="63" x14ac:dyDescent="0.65">
       <c r="A10" s="68" t="s">

--- a/testdata/OpenCart-TestCases.xlsx
+++ b/testdata/OpenCart-TestCases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjectClonned\opencartPlaywrightPythonFramework\opencartPlaywrightPythonFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7004C379-CCF8-491D-9E88-5634EDE2E2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE296E8-8157-49EA-A6E1-79F7CB87DF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="914" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vesion History" sheetId="2" r:id="rId1"/>
@@ -8223,9 +8223,6 @@
     <t>3.docker</t>
   </si>
   <si>
-    <t>6.Execution from Azure</t>
-  </si>
-  <si>
     <t>7.Multimpe Environment Execution</t>
   </si>
   <si>
@@ -8242,6 +8239,9 @@
   </si>
   <si>
     <t>TC007_LoginUsingKeyboardKey</t>
+  </si>
+  <si>
+    <t>6.Execution from AWS, GCP</t>
   </si>
 </sst>
 </file>
@@ -10031,7 +10031,7 @@
         <v>2139</v>
       </c>
       <c r="I1" s="71" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.65">
@@ -10049,7 +10049,7 @@
         <v>23</v>
       </c>
       <c r="I2" s="86" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.65">
@@ -10099,22 +10099,22 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.65">
       <c r="I7" s="71" t="s">
-        <v>2153</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.65">
       <c r="I8" s="84" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.65">
       <c r="I9" s="86" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.65">
       <c r="I14" s="20" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
     </row>
   </sheetData>
@@ -21094,7 +21094,7 @@
         <v>2135</v>
       </c>
       <c r="L9" s="67" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="63" x14ac:dyDescent="0.65">
